--- a/stock_fundamentals.xlsx
+++ b/stock_fundamentals.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tharinduabeysinghe/Documents/Tableau/Investing_dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE14044-E290-CC4E-BFCA-4E48E7BEB236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCA6847-E331-1E43-A602-AFE076369139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="26600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="53">
   <si>
     <t>Ticker</t>
   </si>
@@ -71,6 +84,9 @@
   </si>
   <si>
     <t>fcf_CAGR_3y</t>
+  </si>
+  <si>
+    <t>Buy_Score</t>
   </si>
   <si>
     <t>VOO</t>
@@ -232,11 +248,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -539,10 +556,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -594,19 +614,22 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>638.030029296875</v>
+        <v>594.30999755859375</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>29.339791999999999</v>
+        <v>25.67258</v>
       </c>
       <c r="G2">
         <v>0.03</v>
@@ -614,37 +637,37 @@
       <c r="H2">
         <v>3.7622900000000001</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>1855.1179999999999</v>
       </c>
       <c r="J2">
-        <v>2400.4539989233399</v>
+        <v>22359.665607147221</v>
       </c>
       <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2">
+        <v>0.23920439553612879</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>319.10989379882812</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2">
-        <v>0.23985619814466619</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>342.33999633789062</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
       <c r="D3">
-        <v>28.415016000000001</v>
+        <v>25.01238</v>
       </c>
       <c r="E3">
-        <v>709917343744</v>
+        <v>661744582656</v>
       </c>
       <c r="G3">
         <v>0.03</v>
@@ -652,37 +675,37 @@
       <c r="H3">
         <v>4.0681510000000003</v>
       </c>
-      <c r="I3">
-        <v>1134.1189999999999</v>
+      <c r="I3" s="2">
+        <v>1134.1190000000001</v>
       </c>
       <c r="J3">
-        <v>1392.6907984419861</v>
+        <v>12981.872335675969</v>
       </c>
       <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3">
+        <v>0.13888047252325431</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4">
+        <v>97.305000305175781</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3">
-        <v>0.13915930913701391</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4">
-        <v>108.09999847412109</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
       <c r="D4">
-        <v>34.227055</v>
+        <v>29.224316000000002</v>
       </c>
       <c r="E4">
-        <v>14939419648</v>
+        <v>13447550976</v>
       </c>
       <c r="G4">
         <v>0.04</v>
@@ -690,34 +713,34 @@
       <c r="H4">
         <v>8.4909199999999991</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>676.35799999999995</v>
       </c>
       <c r="J4">
-        <v>917.86843904388422</v>
+        <v>8262.0897319122305</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4">
-        <v>9.1714498292735744E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8.8388091973772315E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>257.83999633789062</v>
+        <v>236.2799987792969</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>33.864310000000003</v>
+        <v>31.433572999999999</v>
       </c>
       <c r="G5">
         <v>0.15</v>
@@ -725,34 +748,34 @@
       <c r="H5">
         <v>1.6020099999999999</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>408.88099999999997</v>
       </c>
       <c r="J5">
-        <v>413.06225253326409</v>
+        <v>3785.2292084442138</v>
       </c>
       <c r="K5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5">
-        <v>4.1273668037020678E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+        <v>4.0494499366849859E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>28.620000839233398</v>
+        <v>30.5</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6">
-        <v>17.681011000000002</v>
+        <v>19.235126000000001</v>
       </c>
       <c r="G6">
         <v>0.06</v>
@@ -760,34 +783,34 @@
       <c r="H6">
         <v>33.354453200000002</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>897.97399999999993</v>
       </c>
       <c r="J6">
-        <v>954.60447857617112</v>
+        <v>10173.108226</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6">
-        <v>9.5385206742495079E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.1088322270412713</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7">
-        <v>32.799999237060547</v>
+        <v>28.979900360107418</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7">
-        <v>35.756360000000001</v>
+        <v>31.072590000000002</v>
       </c>
       <c r="G7">
         <v>0.04</v>
@@ -795,175 +818,178 @@
       <c r="H7">
         <v>10.84689</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>285.49</v>
       </c>
       <c r="J7">
-        <v>355.77798372447972</v>
+        <v>3143.4179141704558</v>
       </c>
       <c r="K7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7">
-        <v>3.5549756253610197E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3.3628382252560769E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8">
-        <v>59.229999542236328</v>
+        <v>61.220001220703118</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8">
-        <v>55.355136999999999</v>
+        <v>52.32479</v>
       </c>
       <c r="E8">
-        <v>54486020096</v>
+        <v>57084628992</v>
       </c>
       <c r="F8">
-        <v>0.80700000000000005</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="H8">
         <v>8.6933899999999991</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>493.524</v>
       </c>
       <c r="J8">
-        <v>514.90948572048183</v>
+        <v>5322.0934641204831</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8">
+        <v>5.6935920797705881E-2</v>
+      </c>
+      <c r="P8">
+        <v>-6.2511737236148113E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>27.385000228881839</v>
+      </c>
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="O8">
-        <v>5.1450363843229083E-2</v>
-      </c>
-      <c r="P8">
-        <v>4.0484482605548378E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="D9">
+        <v>10.492336999999999</v>
+      </c>
+      <c r="E9">
+        <v>29274263552</v>
+      </c>
+      <c r="F9">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="H9">
+        <v>2.8612100000000003</v>
+      </c>
+      <c r="I9" s="2">
+        <v>84.657000000000011</v>
+      </c>
+      <c r="J9">
+        <v>783.54236504878997</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
         <v>31</v>
       </c>
-      <c r="B9">
-        <v>27.809999465942379</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>10.574142999999999</v>
-      </c>
-      <c r="E9">
-        <v>29723643904</v>
-      </c>
-      <c r="F9">
-        <v>0.72</v>
-      </c>
-      <c r="H9">
-        <v>2.8612099999999998</v>
-      </c>
-      <c r="I9">
-        <v>84.657000000000011</v>
-      </c>
-      <c r="J9">
-        <v>79.570248571949008</v>
-      </c>
-      <c r="K9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" t="s">
-        <v>30</v>
-      </c>
       <c r="O9">
-        <v>7.9507531977092687E-3</v>
+        <v>8.3823605013365696E-3</v>
       </c>
       <c r="P9">
-        <v>0.1330326698854094</v>
+        <v>0.27139040279008331</v>
       </c>
       <c r="Q9">
-        <v>0.38485549648960871</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+        <v>8.9180225631910748E-2</v>
+      </c>
+      <c r="R9">
+        <v>0.49536575371023112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10">
-        <v>764.40997314453125</v>
+        <v>691.69000244140625</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>39.852609999999999</v>
+        <v>31.516005</v>
       </c>
       <c r="G10">
         <v>0.1</v>
       </c>
       <c r="H10">
-        <v>0.42109999999999997</v>
-      </c>
-      <c r="I10">
-        <v>326.40499999999997</v>
+        <v>0.42110000000000003</v>
+      </c>
+      <c r="I10" s="2">
+        <v>326.40500000000003</v>
       </c>
       <c r="J10">
-        <v>321.89303969116207</v>
+        <v>2912.7066002807619</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10">
-        <v>3.2163932632819421E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+        <v>3.1160225467394449E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11">
-        <v>470.67001342773438</v>
+        <v>368.3699951171875</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11">
-        <v>33.909942999999998</v>
+        <v>23.067001000000001</v>
       </c>
       <c r="E11">
-        <v>3498568581120</v>
+        <v>2737939415040</v>
       </c>
       <c r="F11">
-        <v>1.073</v>
+        <v>1.1080000000000001</v>
       </c>
       <c r="H11">
         <v>0.80213000000000001</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>326.96899999999999</v>
       </c>
       <c r="J11">
-        <v>377.53853787078862</v>
+        <v>2954.8062418334962</v>
       </c>
       <c r="K11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M11">
         <v>28</v>
@@ -972,7 +998,7 @@
         <v>35</v>
       </c>
       <c r="O11">
-        <v>3.7724096519824772E-2</v>
+        <v>3.1610608737289617E-2</v>
       </c>
       <c r="P11">
         <v>0.1222656895479985</v>
@@ -980,40 +1006,43 @@
       <c r="Q11">
         <v>3.202605420584792E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11">
+        <v>0.23548320000179079</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12">
-        <v>185.80999755859381</v>
+        <v>172.92999267578119</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>45.879010000000001</v>
+        <v>35.21996</v>
       </c>
       <c r="E12">
-        <v>4523916001280</v>
+        <v>4203063541760</v>
       </c>
       <c r="F12">
-        <v>2.3140000000000001</v>
+        <v>2.375</v>
       </c>
       <c r="H12">
         <v>2.3002500000000001</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>236.58099999999999</v>
       </c>
       <c r="J12">
-        <v>427.40944688415527</v>
+        <v>3977.822156524659</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M12">
         <v>35</v>
@@ -1022,48 +1051,51 @@
         <v>50</v>
       </c>
       <c r="O12">
-        <v>4.2707256638423119E-2</v>
+        <v>4.2554864693394728E-2</v>
       </c>
       <c r="P12">
-        <v>0.96922587502425794</v>
+        <v>2.0660722620765331</v>
       </c>
       <c r="Q12">
-        <v>0.95596708025944643</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.9390518269164569</v>
+      </c>
+      <c r="R12">
+        <v>0.57555210354352182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13">
-        <v>354.6099853515625</v>
+        <v>306.55999755859381</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13">
-        <v>74.654730000000001</v>
+        <v>59.752434000000001</v>
       </c>
       <c r="E13">
-        <v>1681303011328</v>
+        <v>1453342588928</v>
       </c>
       <c r="F13">
-        <v>1.218</v>
+        <v>1.2569999999999999</v>
       </c>
       <c r="H13">
         <v>1.2667474000000001</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>257.35000000000002</v>
       </c>
       <c r="J13">
-        <v>449.20127695812988</v>
+        <v>3883.34079851355</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M13">
         <v>24</v>
@@ -1072,7 +1104,7 @@
         <v>30</v>
       </c>
       <c r="O13">
-        <v>4.4884722032262167E-2</v>
+        <v>4.1544100197647718E-2</v>
       </c>
       <c r="P13">
         <v>0.21598171113789169</v>
@@ -1080,40 +1112,43 @@
       <c r="Q13">
         <v>0.1816540426343054</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13">
+        <v>0.16318767361163941</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14">
-        <v>71.239997863769531</v>
+        <v>75.819999694824219</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14">
-        <v>23.589403000000001</v>
+        <v>24.94079</v>
       </c>
       <c r="E14">
-        <v>306593234944</v>
+        <v>326340870144</v>
       </c>
       <c r="F14">
-        <v>0.38700000000000001</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="H14">
         <v>8.9810000000000001E-2</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>6.1959999999999997</v>
       </c>
       <c r="J14">
-        <v>6.3980642081451409</v>
+        <v>68.093941725921638</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M14">
         <v>21</v>
@@ -1122,48 +1157,51 @@
         <v>25</v>
       </c>
       <c r="O14">
-        <v>6.3930213082169821E-4</v>
+        <v>7.2847109864715182E-4</v>
       </c>
       <c r="P14">
-        <v>3.0190473880761019E-2</v>
+        <v>0.1155177614738823</v>
       </c>
       <c r="Q14">
-        <v>-0.25044603875530358</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>-0.17796380006831691</v>
+      </c>
+      <c r="R14">
+        <v>0.52347936052172495</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>333.92999267578119</v>
+        <v>269.239990234375</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15">
-        <v>17.392187</v>
+        <v>20.363461999999998</v>
       </c>
       <c r="E15">
-        <v>302486683648</v>
+        <v>244350861312</v>
       </c>
       <c r="F15">
-        <v>0.42499999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H15">
         <v>0.96377000000000002</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>339.661</v>
       </c>
       <c r="J15">
-        <v>321.83170904113769</v>
+        <v>2594.854253881836</v>
       </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M15">
         <v>18</v>
@@ -1172,48 +1210,51 @@
         <v>22</v>
       </c>
       <c r="O15">
-        <v>3.2157804401846783E-2</v>
+        <v>2.7759831216158781E-2</v>
       </c>
       <c r="P15">
-        <v>-4.9823123496859127E-2</v>
+        <v>-0.14517352798270891</v>
       </c>
       <c r="Q15">
-        <v>1.3493020788259759E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+        <v>-0.1176918367873717</v>
+      </c>
+      <c r="R15">
+        <v>0.22568985862371499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16">
-        <v>335.97000122070312</v>
+        <v>287.17999267578119</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16">
-        <v>33.198616000000001</v>
+        <v>26.59074</v>
       </c>
       <c r="E16">
-        <v>4069309546496</v>
+        <v>3474016436224</v>
       </c>
       <c r="F16">
-        <v>1.0860000000000001</v>
+        <v>1.1120000000000001</v>
       </c>
       <c r="H16">
         <v>0.30099999999999999</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>56.124000000000002</v>
       </c>
       <c r="J16">
-        <v>101.1269703674316</v>
+        <v>864.41177795410147</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M16">
         <v>22</v>
@@ -1222,133 +1263,139 @@
         <v>28</v>
       </c>
       <c r="O16">
-        <v>1.0104726294734171E-2</v>
+        <v>9.2475039865411654E-3</v>
       </c>
       <c r="P16">
-        <v>0.12745113764126351</v>
+        <v>0.33337901890243993</v>
       </c>
       <c r="Q16">
-        <v>2.783009197173469E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+        <v>6.8791402492229148E-2</v>
+      </c>
+      <c r="R16">
+        <v>0.49145987370602012</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17">
-        <v>178.96000671386719</v>
+        <v>146.32000732421881</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17">
-        <v>416.18606999999997</v>
+        <v>232.25398000000001</v>
       </c>
       <c r="E17">
-        <v>426539778048</v>
+        <v>349949984768</v>
       </c>
       <c r="F17">
-        <v>1.5449999999999999</v>
+        <v>1.7390000000000001</v>
       </c>
       <c r="H17">
         <v>0.2</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>23.815999999999999</v>
       </c>
       <c r="J17">
-        <v>35.792001342773439</v>
+        <v>292.6400146484375</v>
       </c>
       <c r="K17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L17" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17">
+        <v>3.130671944900991E-3</v>
+      </c>
+      <c r="Q17">
+        <v>1.252870532084714</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>19.17499923706055</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>15.847106</v>
+      </c>
+      <c r="E18">
+        <v>65968029696</v>
+      </c>
+      <c r="F18">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="H18">
+        <v>12.962710000000001</v>
+      </c>
+      <c r="I18" s="2">
+        <v>257.31</v>
+      </c>
+      <c r="J18">
+        <v>2485.5995436023709</v>
+      </c>
+      <c r="K18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18">
+        <v>2.6591020940055169E-2</v>
+      </c>
+      <c r="P18">
+        <v>-4.7454393547517022E-2</v>
+      </c>
+      <c r="Q18">
+        <v>-0.1213645121172976</v>
+      </c>
+      <c r="R18">
+        <v>0.24856842162090609</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19">
+        <v>331.92001342773438</v>
+      </c>
+      <c r="C19" t="s">
         <v>36</v>
       </c>
-      <c r="O17">
-        <v>3.576379039097174E-3</v>
-      </c>
-      <c r="Q17">
-        <v>0.52588519097337327</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18">
-        <v>17.39999961853027</v>
-      </c>
-      <c r="C18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18">
-        <v>13.92</v>
-      </c>
-      <c r="E18">
-        <v>59740930048</v>
-      </c>
-      <c r="F18">
-        <v>0.66300000000000003</v>
-      </c>
-      <c r="H18">
-        <v>12.96271</v>
-      </c>
-      <c r="I18">
-        <v>257.31</v>
-      </c>
-      <c r="J18">
-        <v>225.5511490551186</v>
-      </c>
-      <c r="K18" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18">
-        <v>2.253733715529925E-2</v>
-      </c>
-      <c r="P18">
-        <v>-0.121821658655534</v>
-      </c>
-      <c r="Q18">
-        <v>-4.1594178160163309E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19">
-        <v>331.20999145507812</v>
-      </c>
-      <c r="C19" t="s">
-        <v>35</v>
-      </c>
       <c r="D19">
-        <v>34.609195999999997</v>
+        <v>32.069564999999997</v>
       </c>
       <c r="E19">
-        <v>1717822160896</v>
+        <v>1721504759808</v>
       </c>
       <c r="F19">
-        <v>1.274</v>
+        <v>1.282</v>
       </c>
       <c r="H19">
         <v>0.21299999999999999</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>64.951999999999998</v>
       </c>
       <c r="J19">
-        <v>70.547728179931639</v>
+        <v>706.98962860107417</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M19">
         <v>15</v>
@@ -1357,48 +1404,51 @@
         <v>20</v>
       </c>
       <c r="O19">
-        <v>7.0492123059101904E-3</v>
+        <v>7.5633969546384872E-3</v>
       </c>
       <c r="P19">
-        <v>0.25285455116292321</v>
+        <v>0.1911504117362903</v>
       </c>
       <c r="Q19">
-        <v>0.48548123284767097</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.23961666265482079</v>
+      </c>
+      <c r="R19">
+        <v>0.51190006799704091</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20">
-        <v>1270.160034179688</v>
+        <v>1303.739990234375</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20">
-        <v>45.057113999999999</v>
+        <v>45.809559999999998</v>
       </c>
       <c r="E20">
-        <v>493009666048</v>
+        <v>511924830208</v>
       </c>
       <c r="F20">
-        <v>1.341</v>
+        <v>1.431</v>
       </c>
       <c r="H20">
         <v>7.7945600000000004E-2</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>85</v>
       </c>
       <c r="J20">
-        <v>99.003385960156251</v>
+        <v>1016.207957828125</v>
       </c>
       <c r="K20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M20">
         <v>30</v>
@@ -1407,48 +1457,51 @@
         <v>40</v>
       </c>
       <c r="O20">
-        <v>9.8925352331279831E-3</v>
+        <v>1.087142422262255E-2</v>
       </c>
       <c r="P20">
-        <v>0.1029402150686083</v>
+        <v>0.17785803341817941</v>
       </c>
       <c r="Q20">
-        <v>-2.84781681744809E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.15442882655428189</v>
+      </c>
+      <c r="R20">
+        <v>0.46679363585416811</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21">
-        <v>631.09002685546875</v>
+        <v>569.0150146484375</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21">
-        <v>27.924337000000001</v>
+        <v>24.223713</v>
       </c>
       <c r="E21">
-        <v>1590679830528</v>
+        <v>1439354978304</v>
       </c>
       <c r="F21">
-        <v>1.2869999999999999</v>
+        <v>1.2789999999999999</v>
       </c>
       <c r="H21">
         <v>0.8361599999999999</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>520.80500000000006</v>
       </c>
       <c r="J21">
-        <v>527.69223685546865</v>
+        <v>4757.8759464843743</v>
       </c>
       <c r="K21" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M21">
         <v>20</v>
@@ -1457,48 +1510,51 @@
         <v>26</v>
       </c>
       <c r="O21">
-        <v>5.2727631431128089E-2</v>
+        <v>5.0899904310326052E-2</v>
       </c>
       <c r="P21">
         <v>0.20109907643223979</v>
       </c>
       <c r="Q21">
-        <v>0.1151379467515707</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+        <v>0.33708391235753271</v>
+      </c>
+      <c r="R21">
+        <v>9.3843759718474876E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22">
-        <v>144.24000549316409</v>
+        <v>143.3999938964844</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22">
-        <v>21.087719</v>
+        <v>21.275964999999999</v>
       </c>
       <c r="E22">
-        <v>337591631872</v>
+        <v>335625584640</v>
       </c>
       <c r="F22">
-        <v>0.38800000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H22">
-        <v>0.10375</v>
-      </c>
-      <c r="I22">
-        <v>14.786</v>
+        <v>0.10375000000000001</v>
+      </c>
+      <c r="I22" s="2">
+        <v>14.786000000000001</v>
       </c>
       <c r="J22">
-        <v>14.96490056991577</v>
+        <v>148.77749366760261</v>
       </c>
       <c r="K22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M22">
         <v>21</v>
@@ -1507,13 +1563,16 @@
         <v>24</v>
       </c>
       <c r="O22">
-        <v>1.495310536224767E-3</v>
+        <v>1.591626237503454E-3</v>
       </c>
       <c r="P22">
         <v>3.8647751796379907E-2</v>
       </c>
       <c r="Q22">
         <v>1.15848859193739E-2</v>
+      </c>
+      <c r="R22">
+        <v>0.52792063299840852</v>
       </c>
     </row>
   </sheetData>
